--- a/docs/data/jp/xlsx/6565.xlsx
+++ b/docs/data/jp/xlsx/6565.xlsx
@@ -8555,7 +8555,7 @@
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>Loss On Changes In Construction Project EL</t>
+          <t>건설 계획 변경 손실</t>
         </is>
       </c>
       <c r="T109" s="22" t="n">
@@ -9464,7 +9464,7 @@
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>Other Extraordinary Loss Income Ope CF</t>
+          <t>기타 특별손익(△는 이익)</t>
         </is>
       </c>
       <c r="O128" s="22" t="n">
@@ -14794,7 +14794,7 @@
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>Deposits For Stores In Preparation</t>
+          <t>점포 임차 가계정</t>
         </is>
       </c>
       <c r="H103" s="22" t="n">
@@ -14804,7 +14804,7 @@
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>Membership</t>
+          <t>회원권</t>
         </is>
       </c>
       <c r="E104" s="22" t="n">
@@ -15597,7 +15597,7 @@
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>Guarantee Deposits Received NCL</t>
+          <t>수입 보증금</t>
         </is>
       </c>
       <c r="H129" s="22" t="n">
@@ -15867,7 +15867,7 @@
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>Reserve For Special Depreciation</t>
+          <t>특별상각 준비금</t>
         </is>
       </c>
       <c r="H138" s="22" t="n">
